--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_51_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_51_IN_Piura.xlsx
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>15.33</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C11" s="29">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>50.04</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>27.8</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>6.83</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1917,11 +1917,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>22.927</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>14.9871</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>65.37</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1967,11 +1967,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>7.9399</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>34.63</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2146,11 +2146,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>22.9315</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2269,6 +2269,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2334,6 +2335,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -2382,6 +2384,7 @@
       <c r="G13" s="8" t="n"/>
       <c r="H13" s="8" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="84" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
@@ -2799,11 +2802,11 @@
       </c>
       <c r="B18" s="31">
         <f>SUM(B10:B17)</f>
-        <v/>
+        <v>523.87</v>
       </c>
       <c r="C18" s="23">
         <f>SUM(C10:C17)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -2813,19 +2816,19 @@
       <c r="E18" s="17" t="inlineStr"/>
       <c r="F18" s="17">
         <f>ROUND(AVERAGE(F10:F17),2)</f>
-        <v/>
+        <v>28.06</v>
       </c>
       <c r="G18" s="22">
         <f>ROUND(AVERAGE(G10:G17),4)</f>
-        <v/>
+        <v>0.5477</v>
       </c>
       <c r="H18" s="23">
         <f>ROUND(AVERAGE(H10:H17),2)</f>
-        <v/>
+        <v>72.48</v>
       </c>
       <c r="I18" s="23">
         <f>ROUND(AVERAGE(I10:I17),2)</f>
-        <v/>
+        <v>31.88</v>
       </c>
     </row>
     <row r="19"/>
@@ -3435,12 +3438,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>15 verificaciones</t>
+          <t>17 verificaciones</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>CONFORME: 4 · CORREGIDO: 1 · NO SUSTANTIVA: 2 · SUSTANTIVA: 8</t>
+          <t>CONFORME: 4 · CORREGIDO: 3 · NO SUSTANTIVA: 2 · SUSTANTIVA: 8</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
